--- a/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
+++ b/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
@@ -1214,4 +1214,10 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{0715da57-2220-4af5-8043-7636ed43cd28}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
+++ b/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
@@ -1218,6 +1218,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{0715da57-2220-4af5-8043-7636ed43cd28}" removed="1"/>
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{524c0344-9201-463e-aea9-4e5b28000606}" removed="1"/>
 </clbl:labelList>
 </file>
--- a/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
+++ b/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
@@ -13,13 +13,13 @@
     <sheet name="인력운영_현황" sheetId="9" r:id="rId9"/>
     <sheet name="인력운영_세부내역" sheetId="10" r:id="rId10"/>
     <sheet name="출장현황" sheetId="11" r:id="rId11"/>
-    <sheet name="주요현안" sheetId="12" r:id="rId12"/>
+    <sheet name="현안" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t xml:space="preserve">플랜트구매품질팀 통합관리 대시보드 - Excel 입력 양식</t>
   </si>
@@ -27,7 +27,7 @@
     <t xml:space="preserve">사용 방법</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 아래 시트탭의 각 시트(프로젝트_현황 / 프로젝트_구매품질 실적 / 프로젝트_NCR처리현황 / PQAN / TPA_목록 / TPA_집행현황 / TPA_월별대금청구현황 / 인력운영_현황 / 인력운영_세부내역 / 출장현황 / 주요현안)에 데이터를 입력합니다.</t>
+    <t xml:space="preserve">1. 아래 시트탭의 각 시트(프로젝트_현황 / 프로젝트_구매품질 실적 / 프로젝트_NCR처리현황 / PQAN / TPA_목록 / TPA_집행현황 / TPA_월별대금청구현황 / 인력운영_현황 / 인력운영_세부내역 / 출장현황 / 현안)에 데이터를 입력합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">2. 1행의 컬럼명(헤더)은 절대 변경하지 마세요. 시트명도 그대로 유지해야 합니다.</t>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">• 출장현황 시트: 출장목적(FAT / PIM / Monitoring / 공장검사 / 업체실사 / 업체감사 / 교육 / 현안미팅)에 따라 색상이 자동 적용됩니다.</t>
   </si>
   <si>
+    <t xml:space="preserve">• 현안 시트: Project_Code / Title / Owner / 등록일 / 종결일 / Status 컬럼. 등록일·종결일·Status는 대시보드에서 직접 편집 후 Excel 재다운로드 시 자동 저장됩니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TPA Warning 기준 (참고)</t>
   </si>
   <si>
@@ -396,16 +399,22 @@
     <t xml:space="preserve">복귀일</t>
   </si>
   <si>
+    <t xml:space="preserve">Project_Code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
     <t xml:space="preserve">Owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Project_Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Action_Required</t>
+    <t xml:space="preserve">등록일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종결일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
   </si>
 </sst>
 </file>
@@ -603,14 +612,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" t="s" s="2">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" t="s" s="0">
         <v>24</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" t="s" s="0">
+    <row r="29"/>
+    <row r="30" ht="17.25" customHeight="1">
+      <c r="A30" t="s" s="2">
         <v>25</v>
       </c>
     </row>
@@ -624,20 +633,25 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34" ht="17.25" customHeight="1">
-      <c r="A34" t="s" s="2">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" t="s" s="0">
         <v>28</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" t="s" s="0">
+    <row r="34"/>
+    <row r="35" ht="17.25" customHeight="1">
+      <c r="A35" t="s" s="2">
         <v>29</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" t="s" s="0">
         <v>30</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" t="s" s="0">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -659,37 +673,37 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -712,28 +726,28 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -744,22 +758,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="E1" t="s" s="3">
+        <v>130</v>
+      </c>
+      <c r="F1" t="s" s="3">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -781,40 +805,40 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -830,43 +854,43 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M1" t="s" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -901,61 +925,61 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M1" t="s" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N1" t="s" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O1" t="s" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P1" t="s" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q1" t="s" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R1" t="s" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S1" t="s" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -982,70 +1006,70 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="J1" t="s" s="3">
         <v>56</v>
       </c>
-      <c r="J1" t="s" s="3">
-        <v>55</v>
-      </c>
       <c r="K1" t="s" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M1" t="s" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N1" t="s" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O1" t="s" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P1" t="s" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q1" t="s" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R1" t="s" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S1" t="s" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="T1" t="s" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U1" t="s" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="V1" t="s" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1065,19 +1089,19 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1094,34 +1118,34 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1142,22 +1166,22 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1182,42 +1206,36 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{524c0344-9201-463e-aea9-4e5b28000606}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
+++ b/Template_플랜트구매품질팀 통합관리 대시보드_Raw File.xlsx
@@ -1238,4 +1238,10 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{5a448e17-ae46-401b-817e-3a9d843c388d}" removed="1"/>
+</clbl:labelList>
 </file>